--- a/docs/gini-flow/billing-template.xlsx
+++ b/docs/gini-flow/billing-template.xlsx
@@ -559,7 +559,7 @@
     <t>Follow Up</t>
   </si>
   <si>
-    <t>Test items only (required for them): the test's name exactly as in the test catalogue list you were given.</t>
+    <t>Test items only (required for them): the test's name exactly as in Scribe's test catalogue. A test that is only in the lab report catalogue must be added to the test catalogue by an admin first.</t>
   </si>
   <si>
     <t>not a test item</t>
@@ -2789,7 +2789,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="62" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="48" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>154</v>
       </c>

--- a/docs/gini-flow/billing-template.xlsx
+++ b/docs/gini-flow/billing-template.xlsx
@@ -19,8 +19,59 @@
 </workbook>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Available after Phase 3: rows on this sheet are not imported yet. You can fill it in now; it is read once payment rules and discounts are switched on.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Available after Phase 3: rows on this sheet are not imported yet. You can fill it in now; it is read once payment rules and discounts are switched on.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Available after Phase 3: rows on this sheet are not imported yet. You can fill it in now; it is read once payment rules and discounts are switched on.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="332">
   <si>
     <t>group_code</t>
   </si>
@@ -316,6 +367,12 @@
     <t>Any error stops the whole upload: fix the rows listed in the error file and upload again.</t>
   </si>
   <si>
+    <t>Rule 15</t>
+  </si>
+  <si>
+    <t>The Payment rules, Consultant fees and Discounts sheets are available after Phase 3. Their tabs are grey and rows on them are not imported yet; fill them in now if you like, and upload again once they are switched on.</t>
+  </si>
+  <si>
     <t>Allowed values</t>
   </si>
   <si>
@@ -725,6 +782,12 @@
   </si>
   <si>
     <t>What a category's patient pays at the counter, for a whole group, a subgroup or one item. No rule = the patient pays in full.</t>
+  </si>
+  <si>
+    <t>(available after Phase 3)</t>
+  </si>
+  <si>
+    <t>Available after Phase 3: rows on this sheet are not imported yet. You can fill it in now; it is read once payment rules and discounts are switched on.</t>
   </si>
   <si>
     <t>The category or sub-category the rule is for.</t>
@@ -1041,7 +1104,7 @@
       <color rgb="FF4F595C"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1068,6 +1131,11 @@
         <fgColor rgb="FFF1EFE9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1088,7 +1156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1122,6 +1190,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1501,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1893,43 +1964,43 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="20" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="C20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="F20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>38</v>
@@ -1950,9 +2021,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>38</v>
@@ -1975,7 +2046,7 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>38</v>
@@ -1996,12 +2067,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>70</v>
@@ -2019,9 +2090,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>40</v>
@@ -2044,10 +2115,10 @@
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>70</v>
@@ -2067,7 +2138,7 @@
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>43</v>
@@ -2076,30 +2147,30 @@
         <v>70</v>
       </c>
       <c r="D29" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>116</v>
@@ -2113,7 +2184,7 @@
     </row>
     <row r="31" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>30</v>
@@ -2122,10 +2193,10 @@
         <v>70</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>70</v>
@@ -2136,56 +2207,56 @@
     </row>
     <row r="32" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="F32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="C33" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="F33" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>13</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>70</v>
@@ -2203,12 +2274,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>70</v>
@@ -2226,104 +2297,104 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="F36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="C37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-    </row>
-    <row r="39" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
+      <c r="E37" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="F37" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="13" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+    </row>
+    <row r="40" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="11" t="s">
+      <c r="B40" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="C40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E40" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>139</v>
+      <c r="F40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E41" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>141</v>
@@ -2331,384 +2402,384 @@
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="F42" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="11">
-        <v>20</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>146</v>
       </c>
       <c r="F43" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G43" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B45" s="11" t="s">
+      <c r="C45" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="C46" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>136</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>151</v>
       </c>
       <c r="F46" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G46" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="E47" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>138</v>
-      </c>
       <c r="G47" s="11" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>153</v>
-      </c>
       <c r="F48" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G48" s="11">
-        <v>10</v>
+        <v>140</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="G49" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="C50" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G49" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G51" s="11" t="s">
+      <c r="C51" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>157</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>158</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="53" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>160</v>
       </c>
       <c r="F53" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G53" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>143</v>
-      </c>
       <c r="E54" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G54" s="11">
-        <v>500</v>
+        <v>140</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>163</v>
+        <v>140</v>
+      </c>
+      <c r="G55" s="11">
+        <v>500</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>164</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G57" s="11">
-        <v>5</v>
+        <v>144</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>167</v>
@@ -2716,465 +2787,465 @@
       <c r="F58" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" s="11" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="59" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59" s="11" t="s">
+      <c r="F59" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="60" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>172</v>
       </c>
       <c r="F60" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G60" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G60" s="11" t="s">
+    </row>
+    <row r="61" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="11" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="61" ht="48" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D61" s="11" t="s">
+      <c r="F61" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="G61" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B62" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="G62" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B63" s="11" t="s">
+      <c r="C63" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F63" s="11" t="s">
+      <c r="C64" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="65" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G63" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="64" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" ht="48" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B65" s="11" t="s">
+      <c r="C65" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G65" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F65" s="11" t="s">
+      <c r="C66" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>136</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>185</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="67" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>187</v>
       </c>
       <c r="F67" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G67" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="68" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B68" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="69" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B69" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="G68" s="11" t="s">
+      <c r="C69" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="69" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E69" s="11" t="s">
+      <c r="F69" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="F69" s="11" t="s">
-        <v>142</v>
-      </c>
       <c r="G69" s="11" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B71" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F71" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="72" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="C72" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B73" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>24</v>
-      </c>
       <c r="C74" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>199</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B75" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B76" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F75" s="11" t="s">
+      <c r="C76" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B77" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="76" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G77" s="11" t="s">
+      <c r="C77" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E77" s="13" t="s">
         <v>203</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>204</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G78" s="11" t="s">
         <v>205</v>
@@ -3182,39 +3253,39 @@
     </row>
     <row r="79" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>206</v>
       </c>
       <c r="F79" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G79" s="11" t="s">
         <v>207</v>
-      </c>
-      <c r="G79" s="11">
-        <v>60</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>208</v>
@@ -3222,22 +3293,22 @@
       <c r="F80" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="G80" s="11" t="s">
-        <v>169</v>
+      <c r="G80" s="11">
+        <v>60</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>210</v>
@@ -3246,228 +3317,228 @@
         <v>211</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>212</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="83" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>214</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="84" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G84" s="11">
-        <v>100</v>
+        <v>140</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B85" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G85" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B86" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C85" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F85" s="11" t="s">
+      <c r="C86" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="87" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G85" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="86" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G86" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G87" s="11" t="s">
-        <v>189</v>
+      <c r="C87" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B88" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="F88" s="11" t="s">
+      <c r="C89" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D89" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="89" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>222</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>223</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>224</v>
       </c>
       <c r="F90" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G90" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="G90" s="11">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>226</v>
@@ -3475,22 +3546,22 @@
       <c r="F91" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="G91" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="92" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G91" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>228</v>
@@ -3499,248 +3570,248 @@
         <v>229</v>
       </c>
       <c r="G92" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E93" s="11" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="93" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B93" s="11" t="s">
+      <c r="F93" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C93" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="G93" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="94" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="13" t="s">
+      <c r="C94" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E94" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="B94" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E94" s="13" t="s">
+      <c r="F94" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="F94" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B95" s="11" t="s">
+      <c r="G94" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B97" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="F95" s="11" t="s">
+      <c r="C97" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D97" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G95" s="11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E96" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="F96" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G96" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="97" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="E97" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>243</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>244</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D101" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E101" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="F101" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G101" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E102" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="F101" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G101" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="102" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E102" s="11" t="s">
+      <c r="F102" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="F102" s="11" t="s">
+      <c r="G102" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="G102" s="11">
-        <v>20</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>249</v>
@@ -3749,24 +3820,24 @@
         <v>250</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="104" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="E104" s="11" t="s">
         <v>251</v>
@@ -3774,1405 +3845,1497 @@
       <c r="F104" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G104" s="11" t="s">
-        <v>169</v>
+      <c r="G104" s="11">
+        <v>20</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="106" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B107" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G107" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E108" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G108" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F107" s="11" t="s">
+      <c r="C109" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E109" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G109" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="110" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B110" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G107" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="108" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="B108" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E108" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="F108" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G108" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B109" s="11" t="s">
+      <c r="C110" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G110" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111" ht="48" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G111" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B112" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C109" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E109" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="F109" s="11" t="s">
+      <c r="C112" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D112" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G109" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="110" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B110" s="11" t="s">
+      <c r="E112" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G112" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="113" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B113" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C110" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="E110" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="G110" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E111" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G111" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="C113" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>262</v>
       </c>
       <c r="F113" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G113" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D114" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G113" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="114" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>143</v>
-      </c>
       <c r="E114" s="11" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>248</v>
+        <v>140</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>249</v>
+        <v>145</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>108</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="118" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>267</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>252</v>
+        <v>140</v>
       </c>
       <c r="G118" s="11" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>268</v>
       </c>
       <c r="F119" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G119" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="G120" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="G119" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="B120" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C120" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="F120" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G120" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>271</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="G121" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E122" s="11" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="122" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B122" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E122" s="11" t="s">
+      <c r="F122" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G122" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="123" ht="33" customHeight="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="F122" s="11" t="s">
+      <c r="B123" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E123" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="G122" s="11" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="F123" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G123" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="124" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E124" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="F124" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G124" s="11" t="s">
-        <v>104</v>
+      <c r="F123" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124" ht="48" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="B124" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E124" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G124" s="15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E125" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G125" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="126" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E126" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="G126" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G125" s="11">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B126" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E126" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="F126" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="G126" s="11">
-        <v>300</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="E127" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G127" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="128" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E128" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="F127" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="G127" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B128" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>285</v>
-      </c>
       <c r="F128" s="11" t="s">
-        <v>283</v>
+        <v>140</v>
       </c>
       <c r="G128" s="11" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="G129" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="130" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="G129" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="G130" s="11" t="s">
-        <v>289</v>
+        <v>285</v>
+      </c>
+      <c r="G130" s="11">
+        <v>300</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="132" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G132" s="11" t="s">
-        <v>293</v>
+        <v>171</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="134" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>209</v>
+        <v>292</v>
       </c>
       <c r="G134" s="11" t="s">
-        <v>169</v>
+        <v>293</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>210</v>
+        <v>294</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="136" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="136" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="E136" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="F136" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="F136" s="11" t="s">
-        <v>252</v>
-      </c>
       <c r="G136" s="11" t="s">
-        <v>223</v>
+        <v>297</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="G137" s="11" t="s">
-        <v>298</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E138" s="11" t="s">
         <v>299</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="G138" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E139" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="G139" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="140" ht="63" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E140" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="F139" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G139" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C140" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D140" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E140" s="11" t="s">
-        <v>301</v>
-      </c>
       <c r="F140" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G140" s="11">
-        <v>10</v>
+        <v>256</v>
+      </c>
+      <c r="G140" s="11" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="E141" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G141" s="11" t="s">
         <v>302</v>
-      </c>
-      <c r="F141" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G141" s="11" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E142" s="11" t="s">
         <v>303</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="G142" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="143" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E143" s="11" t="s">
         <v>304</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G143" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="G143" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E144" s="11" t="s">
         <v>305</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G144" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="145" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="G144" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E145" s="11" t="s">
         <v>306</v>
       </c>
       <c r="F145" s="11" t="s">
-        <v>307</v>
+        <v>168</v>
       </c>
       <c r="G145" s="11" t="s">
-        <v>308</v>
+        <v>171</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B146" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G146" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="147" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E147" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F147" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G147" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="148" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E148" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="F148" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G148" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="149" ht="33" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E149" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="G149" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B150" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C146" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D146" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E146" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F146" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G146" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="B148" s="10"/>
-      <c r="C148" s="10"/>
-      <c r="D148" s="10"/>
-      <c r="E148" s="10"/>
-      <c r="F148" s="10"/>
-      <c r="G148" s="10"/>
-    </row>
-    <row r="149" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B149" s="14"/>
-      <c r="C149" s="14"/>
-      <c r="D149" s="14"/>
-      <c r="E149" s="14"/>
-      <c r="F149" s="14"/>
-      <c r="G149" s="14"/>
-    </row>
-    <row r="151" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="B151" s="10"/>
-      <c r="C151" s="10"/>
-      <c r="D151" s="10"/>
-      <c r="E151" s="10"/>
-      <c r="F151" s="10"/>
-      <c r="G151" s="10"/>
-    </row>
-    <row r="152" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+      <c r="C150" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E150" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F150" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G150" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B152" s="10"/>
+      <c r="C152" s="10"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
+      <c r="G152" s="10"/>
+    </row>
+    <row r="153" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="14"/>
+      <c r="E153" s="14"/>
+      <c r="F153" s="14"/>
+      <c r="G153" s="14"/>
+    </row>
+    <row r="155" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B155" s="10"/>
+      <c r="C155" s="10"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
+    </row>
+    <row r="156" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B156" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C152" s="7" t="s">
+      <c r="C156" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="D156" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="E156" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="F156" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G152" s="7" t="s">
+      <c r="G156" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="H156" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="I156" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="J156" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="K156" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>312</v>
-      </c>
-      <c r="B153" t="s">
-        <v>313</v>
-      </c>
-      <c r="C153" t="s">
-        <v>70</v>
-      </c>
-      <c r="D153" t="s">
-        <v>314</v>
-      </c>
-      <c r="E153" t="s">
-        <v>135</v>
-      </c>
-      <c r="F153" t="s">
-        <v>142</v>
-      </c>
-      <c r="G153" t="s">
-        <v>142</v>
-      </c>
-      <c r="H153" t="s">
-        <v>135</v>
-      </c>
-      <c r="I153" t="s">
-        <v>70</v>
-      </c>
-      <c r="J153" t="s">
-        <v>70</v>
-      </c>
-      <c r="K153" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>315</v>
-      </c>
-      <c r="B154" t="s">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>316</v>
       </c>
-      <c r="C154" t="s">
-        <v>312</v>
-      </c>
-      <c r="D154" t="s">
-        <v>70</v>
-      </c>
-      <c r="E154" t="s">
-        <v>135</v>
-      </c>
-      <c r="F154" t="s">
-        <v>142</v>
-      </c>
-      <c r="G154" t="s">
-        <v>142</v>
-      </c>
-      <c r="H154" t="s">
-        <v>135</v>
-      </c>
-      <c r="I154" t="s">
-        <v>70</v>
-      </c>
-      <c r="J154" t="s">
-        <v>70</v>
-      </c>
-      <c r="K154" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="B157" t="s">
         <v>317</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C157" t="s">
+        <v>70</v>
+      </c>
+      <c r="D157" t="s">
         <v>318</v>
       </c>
-      <c r="C155" t="s">
-        <v>312</v>
-      </c>
-      <c r="D155" t="s">
-        <v>70</v>
-      </c>
-      <c r="E155" t="s">
-        <v>135</v>
-      </c>
-      <c r="F155" t="s">
-        <v>135</v>
-      </c>
-      <c r="G155" t="s">
-        <v>142</v>
-      </c>
-      <c r="H155" t="s">
-        <v>135</v>
-      </c>
-      <c r="I155" t="s">
-        <v>70</v>
-      </c>
-      <c r="J155" t="s">
-        <v>70</v>
-      </c>
-      <c r="K155" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="E157" t="s">
+        <v>137</v>
+      </c>
+      <c r="F157" t="s">
+        <v>144</v>
+      </c>
+      <c r="G157" t="s">
+        <v>144</v>
+      </c>
+      <c r="H157" t="s">
+        <v>137</v>
+      </c>
+      <c r="I157" t="s">
+        <v>70</v>
+      </c>
+      <c r="J157" t="s">
+        <v>70</v>
+      </c>
+      <c r="K157" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>319</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B158" t="s">
         <v>320</v>
       </c>
-      <c r="C156" t="s">
-        <v>312</v>
-      </c>
-      <c r="D156" t="s">
-        <v>70</v>
-      </c>
-      <c r="E156" t="s">
-        <v>135</v>
-      </c>
-      <c r="F156" t="s">
-        <v>142</v>
-      </c>
-      <c r="G156" t="s">
-        <v>142</v>
-      </c>
-      <c r="H156" t="s">
-        <v>135</v>
-      </c>
-      <c r="I156" t="s">
-        <v>70</v>
-      </c>
-      <c r="J156" t="s">
-        <v>70</v>
-      </c>
-      <c r="K156" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="157" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="15" t="s">
+      <c r="C158" t="s">
+        <v>316</v>
+      </c>
+      <c r="D158" t="s">
+        <v>70</v>
+      </c>
+      <c r="E158" t="s">
+        <v>137</v>
+      </c>
+      <c r="F158" t="s">
+        <v>144</v>
+      </c>
+      <c r="G158" t="s">
+        <v>144</v>
+      </c>
+      <c r="H158" t="s">
+        <v>137</v>
+      </c>
+      <c r="I158" t="s">
+        <v>70</v>
+      </c>
+      <c r="J158" t="s">
+        <v>70</v>
+      </c>
+      <c r="K158" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>321</v>
       </c>
-      <c r="B157" s="15"/>
-      <c r="C157" s="15"/>
-      <c r="D157" s="15"/>
-      <c r="E157" s="15"/>
-      <c r="F157" s="15"/>
-      <c r="G157" s="15"/>
-    </row>
-    <row r="159" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="10" t="s">
+      <c r="B159" t="s">
         <v>322</v>
       </c>
-      <c r="B159" s="10"/>
-      <c r="C159" s="10"/>
-      <c r="D159" s="10"/>
-      <c r="E159" s="10"/>
-      <c r="F159" s="10"/>
-      <c r="G159" s="10"/>
-    </row>
-    <row r="160" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="7" t="s">
+      <c r="C159" t="s">
+        <v>316</v>
+      </c>
+      <c r="D159" t="s">
+        <v>70</v>
+      </c>
+      <c r="E159" t="s">
+        <v>137</v>
+      </c>
+      <c r="F159" t="s">
+        <v>137</v>
+      </c>
+      <c r="G159" t="s">
+        <v>144</v>
+      </c>
+      <c r="H159" t="s">
+        <v>137</v>
+      </c>
+      <c r="I159" t="s">
+        <v>70</v>
+      </c>
+      <c r="J159" t="s">
+        <v>70</v>
+      </c>
+      <c r="K159" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>323</v>
+      </c>
+      <c r="B160" t="s">
+        <v>324</v>
+      </c>
+      <c r="C160" t="s">
+        <v>316</v>
+      </c>
+      <c r="D160" t="s">
+        <v>70</v>
+      </c>
+      <c r="E160" t="s">
+        <v>137</v>
+      </c>
+      <c r="F160" t="s">
+        <v>144</v>
+      </c>
+      <c r="G160" t="s">
+        <v>144</v>
+      </c>
+      <c r="H160" t="s">
+        <v>137</v>
+      </c>
+      <c r="I160" t="s">
+        <v>70</v>
+      </c>
+      <c r="J160" t="s">
+        <v>70</v>
+      </c>
+      <c r="K160" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="161" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="B161" s="16"/>
+      <c r="C161" s="16"/>
+      <c r="D161" s="16"/>
+      <c r="E161" s="16"/>
+      <c r="F161" s="16"/>
+      <c r="G161" s="16"/>
+    </row>
+    <row r="163" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B163" s="10"/>
+      <c r="C163" s="10"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="10"/>
+      <c r="F163" s="10"/>
+      <c r="G163" s="10"/>
+    </row>
+    <row r="164" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B164" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C160" s="7" t="s">
+      <c r="C164" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="D164" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E164" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F160" s="7" t="s">
+      <c r="F164" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G160" s="7" t="s">
+      <c r="G164" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H160" s="7" t="s">
+      <c r="H164" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I160" s="7" t="s">
+      <c r="I164" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J160" s="7" t="s">
+      <c r="J164" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K160" s="7" t="s">
+      <c r="K164" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>327</v>
+      </c>
+      <c r="B165" t="s">
+        <v>70</v>
+      </c>
+      <c r="C165" t="s">
         <v>323</v>
       </c>
-      <c r="B161" t="s">
-        <v>70</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="D165" t="s">
+        <v>265</v>
+      </c>
+      <c r="E165" t="s">
+        <v>108</v>
+      </c>
+      <c r="F165" t="s">
+        <v>70</v>
+      </c>
+      <c r="G165" t="s">
+        <v>110</v>
+      </c>
+      <c r="H165" t="s">
+        <v>70</v>
+      </c>
+      <c r="I165" t="s">
+        <v>70</v>
+      </c>
+      <c r="J165" t="s">
+        <v>70</v>
+      </c>
+      <c r="K165" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>328</v>
+      </c>
+      <c r="B166" t="s">
+        <v>70</v>
+      </c>
+      <c r="C166" t="s">
+        <v>323</v>
+      </c>
+      <c r="D166" t="s">
+        <v>265</v>
+      </c>
+      <c r="E166" t="s">
+        <v>108</v>
+      </c>
+      <c r="F166" t="s">
+        <v>70</v>
+      </c>
+      <c r="G166" t="s">
+        <v>110</v>
+      </c>
+      <c r="H166" t="s">
+        <v>70</v>
+      </c>
+      <c r="I166" t="s">
+        <v>232</v>
+      </c>
+      <c r="J166" t="s">
+        <v>70</v>
+      </c>
+      <c r="K166" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>328</v>
+      </c>
+      <c r="B167" t="s">
+        <v>329</v>
+      </c>
+      <c r="C167" t="s">
         <v>319</v>
       </c>
-      <c r="D161" t="s">
-        <v>261</v>
-      </c>
-      <c r="E161" t="s">
-        <v>106</v>
-      </c>
-      <c r="F161" t="s">
-        <v>70</v>
-      </c>
-      <c r="G161" t="s">
-        <v>108</v>
-      </c>
-      <c r="H161" t="s">
-        <v>70</v>
-      </c>
-      <c r="I161" t="s">
-        <v>70</v>
-      </c>
-      <c r="J161" t="s">
-        <v>70</v>
-      </c>
-      <c r="K161" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>324</v>
-      </c>
-      <c r="B162" t="s">
-        <v>70</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="D167" t="s">
+        <v>265</v>
+      </c>
+      <c r="E167" t="s">
+        <v>104</v>
+      </c>
+      <c r="F167" t="s">
+        <v>330</v>
+      </c>
+      <c r="G167" t="s">
+        <v>110</v>
+      </c>
+      <c r="H167" t="s">
+        <v>70</v>
+      </c>
+      <c r="I167" t="s">
+        <v>232</v>
+      </c>
+      <c r="J167" t="s">
+        <v>70</v>
+      </c>
+      <c r="K167" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>328</v>
+      </c>
+      <c r="B168" t="s">
+        <v>180</v>
+      </c>
+      <c r="C168" t="s">
         <v>319</v>
       </c>
-      <c r="D162" t="s">
-        <v>261</v>
-      </c>
-      <c r="E162" t="s">
-        <v>106</v>
-      </c>
-      <c r="F162" t="s">
-        <v>70</v>
-      </c>
-      <c r="G162" t="s">
-        <v>108</v>
-      </c>
-      <c r="H162" t="s">
-        <v>70</v>
-      </c>
-      <c r="I162" t="s">
-        <v>230</v>
-      </c>
-      <c r="J162" t="s">
-        <v>70</v>
-      </c>
-      <c r="K162" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>324</v>
-      </c>
-      <c r="B163" t="s">
-        <v>325</v>
-      </c>
-      <c r="C163" t="s">
-        <v>315</v>
-      </c>
-      <c r="D163" t="s">
-        <v>261</v>
-      </c>
-      <c r="E163" t="s">
-        <v>102</v>
-      </c>
-      <c r="F163" t="s">
-        <v>326</v>
-      </c>
-      <c r="G163" t="s">
-        <v>108</v>
-      </c>
-      <c r="H163" t="s">
-        <v>70</v>
-      </c>
-      <c r="I163" t="s">
-        <v>230</v>
-      </c>
-      <c r="J163" t="s">
-        <v>70</v>
-      </c>
-      <c r="K163" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>324</v>
-      </c>
-      <c r="B164" t="s">
-        <v>178</v>
-      </c>
-      <c r="C164" t="s">
-        <v>315</v>
-      </c>
-      <c r="D164" t="s">
-        <v>261</v>
-      </c>
-      <c r="E164" t="s">
-        <v>102</v>
-      </c>
-      <c r="F164" t="s">
-        <v>326</v>
-      </c>
-      <c r="G164" t="s">
-        <v>108</v>
-      </c>
-      <c r="H164" t="s">
-        <v>70</v>
-      </c>
-      <c r="I164" t="s">
-        <v>230</v>
-      </c>
-      <c r="J164" t="s">
-        <v>70</v>
-      </c>
-      <c r="K164" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="165" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="B165" s="15"/>
-      <c r="C165" s="15"/>
-      <c r="D165" s="15"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="15"/>
-      <c r="G165" s="15"/>
+      <c r="D168" t="s">
+        <v>265</v>
+      </c>
+      <c r="E168" t="s">
+        <v>104</v>
+      </c>
+      <c r="F168" t="s">
+        <v>330</v>
+      </c>
+      <c r="G168" t="s">
+        <v>110</v>
+      </c>
+      <c r="H168" t="s">
+        <v>70</v>
+      </c>
+      <c r="I168" t="s">
+        <v>232</v>
+      </c>
+      <c r="J168" t="s">
+        <v>70</v>
+      </c>
+      <c r="K168" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="169" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="B169" s="16"/>
+      <c r="C169" s="16"/>
+      <c r="D169" s="16"/>
+      <c r="E169" s="16"/>
+      <c r="F169" s="16"/>
+      <c r="G169" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A148:G148"/>
-    <mergeCell ref="A149:G149"/>
-    <mergeCell ref="A151:G151"/>
-    <mergeCell ref="A157:G157"/>
-    <mergeCell ref="A159:G159"/>
-    <mergeCell ref="A165:G165"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A152:G152"/>
+    <mergeCell ref="A153:G153"/>
+    <mergeCell ref="A155:G155"/>
+    <mergeCell ref="A161:G161"/>
+    <mergeCell ref="A163:G163"/>
+    <mergeCell ref="A169:G169"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5480,6 +5643,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFB0B0B0"/>
+  </sheetPr>
   <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -5551,11 +5717,15 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFB0B0B0"/>
+  </sheetPr>
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -5617,11 +5787,15 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFB0B0B0"/>
+  </sheetPr>
   <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -5748,5 +5922,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/gini-flow/billing-template.xlsx
+++ b/docs/gini-flow/billing-template.xlsx
@@ -361,7 +361,7 @@
     <t>Gini Scribe — billing data template</t>
   </si>
   <si>
-    <t>Fill the sheets, then upload the file in Settings › Billing › Bulk import. Nothing is saved until every row passes the checks.</t>
+    <t>Fill the sheets, then upload the file in Settings › Billing › Bulk import. Every row is checked and listed as Ready, Needs override, Failed or Unchanged; nothing is saved until you press Commit.</t>
   </si>
   <si>
     <t>How to fill this file</t>
@@ -466,7 +466,7 @@
     <t>Rule 16</t>
   </si>
   <si>
-    <t>Any error stops the whole upload: fix the rows listed in the error file and upload again.</t>
+    <t>A row with an error fails and is skipped, and so is every new row that depends on it; the other rows can still be saved. A change to a row already in Scribe is saved only if you choose Override for it — otherwise the row is kept as it is. Download the failed rows, fix them and upload that file again.</t>
   </si>
   <si>
     <t>Allowed values</t>
@@ -2064,7 +2064,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" ht="33" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="78" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>115</v>
       </c>

--- a/docs/gini-flow/billing-template.xlsx
+++ b/docs/gini-flow/billing-template.xlsx
@@ -400,7 +400,7 @@
     <t>Rule 5</t>
   </si>
   <si>
-    <t>There are no packages. Each ordered test is always billed on its own line at its own price.</t>
+    <t>Each ordered test is always billed on its own line. A package (e.g. ABI + VPT at one combined price) is an automatic discount set up on the Discounts page, not an import row.</t>
   </si>
   <si>
     <t>Rule 6</t>
@@ -1811,7 +1811,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="48" customHeight="1" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>115</v>
       </c>
